--- a/output/pdf_financials_xlsx/PGZ.xlsx
+++ b/output/pdf_financials_xlsx/PGZ.xlsx
@@ -5880,49 +5880,49 @@
         <v>0.399707</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.722575</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.512865</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.512865</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.512865</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.512865</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.028178</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.662598</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.236968</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.549299</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.580131</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.421</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.055</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>9.01</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>9.566000000000001</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="93">
@@ -9542,7 +9542,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10528,7 +10532,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11726,7 +11734,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12906,7 +12918,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -14080,7 +14096,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -14783,7 +14803,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -15482,7 +15506,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -16274,7 +16302,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -16569,7 +16601,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -17137,7 +17173,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>0.108414</v>
       </c>
@@ -37320,7 +37360,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PGZ.xlsx
+++ b/output/pdf_financials_xlsx/PGZ.xlsx
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02822</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00062</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.011367</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005163</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1073,19 +1073,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="13">
@@ -1979,19 +1979,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.444235</v>
+        <v>-0.416015</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.032469</v>
+        <v>-1.033089</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.821465</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.298879</v>
+        <v>-4.310246</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.066777</v>
+        <v>-2.07194</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.638054</v>
@@ -2015,19 +2015,19 @@
         <v>-4.553036</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-9.058999999999999</v>
+        <v>-9.089</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-10.153</v>
+        <v>-10.324</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-10.777</v>
+        <v>-10.87</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-6.006</v>
+        <v>-6.091</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="28">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.444235</v>
+        <v>-0.416015</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.032469</v>
+        <v>-1.033089</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.821465</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.298879</v>
+        <v>-4.310246</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.066777</v>
+        <v>-2.07194</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.638054</v>
@@ -2131,19 +2131,19 @@
         <v>-4.5354</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-9.048999999999999</v>
+        <v>-9.079000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-10.146</v>
+        <v>-10.317</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-10.777</v>
+        <v>-10.87</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-6.006</v>
+        <v>-6.091</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="30">
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.956101</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.549065</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.224942</v>
@@ -2417,25 +2417,25 @@
         <v>0.108838</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.049086</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.013948</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.032087</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.800082</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.485441</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.119914</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.89729</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>15.499</v>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.956101</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.549065</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.224942</v>
@@ -2533,25 +2533,25 @@
         <v>0.108838</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.049086</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.013948</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.032087</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.800082</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.485441</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.119914</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.89729</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>15.499</v>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.956101</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.592123</v>
+        <v>0.043058</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.55853</v>
@@ -3229,25 +3229,25 @@
         <v>0.218206</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.049086</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.013948</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.032087</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.88467</v>
+        <v>0.084588</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.516782</v>
+        <v>0.031341</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.122327</v>
+        <v>0.002413</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.938437</v>
+        <v>0.041147</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.093</v>
@@ -7713,16 +7713,16 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018985</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019723</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>0</v>
@@ -7771,16 +7771,16 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018985</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019723</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -9014,7 +9014,11 @@
           <t>Reclamation deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -10227,7 +10231,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -11839,7 +11847,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
@@ -12120,7 +12128,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -14403,7 +14415,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -17276,7 +17288,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -19081,7 +19093,11 @@
           <t>Reclamation deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -21451,7 +21467,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -23263,7 +23283,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -23560,7 +23584,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -40460,7 +40488,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -47447,7 +47475,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -48544,7 +48572,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E407" s="5" t="n">

--- a/output/pdf_financials_xlsx/PGZ.xlsx
+++ b/output/pdf_financials_xlsx/PGZ.xlsx
@@ -783,19 +783,19 @@
         <v>0.49074</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.584</v>
+        <v>0.668</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.15</v>
+        <v>1.232</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.421</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.048</v>
+        <v>1.19</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.572</v>
+        <v>1.715</v>
       </c>
     </row>
     <row r="8">
@@ -969,7 +969,7 @@
         <v>2.262</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1.709</v>
+        <v>1.852</v>
       </c>
     </row>
     <row r="11">
@@ -4350,55 +4350,55 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0168</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.03662</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0805</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.1145</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.181</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.0605</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.0825</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.541</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="68">
@@ -4554,13 +4554,13 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.017155</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.01058</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
@@ -4612,13 +4612,13 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.017155</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.01058</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0</v>
@@ -4844,13 +4844,13 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.017155</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.01058</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.007197</v>
+        <v>0.000197</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
@@ -5176,15 +5176,13 @@
         </is>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.005693461501316322</v>
+        <v>0.01134802828502972</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.001370332123883964</v>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003240815141648426</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.0003858237336713884</v>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
@@ -6897,13 +6895,13 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.002628</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.001682</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.000754</v>
       </c>
       <c r="O110" s="3" t="n">
         <v>0</v>
@@ -11641,7 +11639,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -12433,7 +12435,11 @@
           <t>Lease liabilities (Note 7)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -20045,7 +20051,11 @@
           <t>Private placement (Note 8) 60,419,328 6,948 302</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -22172,7 +22182,11 @@
           <t>Private placement (Note 9) 30,350,000 5,463 607</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -22677,7 +22691,11 @@
           <t>Private placement (Note 9) 60,419,328 6,948 302</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -24188,7 +24206,11 @@
           <t>Private placement (Note 8) 30,350,000 5,463 607</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -24774,7 +24796,11 @@
           <t>Brokered private placement</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -26378,7 +26404,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -39608,7 +39638,11 @@
           <t>Directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -41074,7 +41108,11 @@
           <t>Directors’ fees (Note 10)</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
